--- a/AAII_Financials/Yearly/MTEN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MTEN_YR_FIN.xlsx
@@ -1782,7 +1782,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
@@ -2142,7 +2142,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="E57" s="3">
         <v>1500</v>
@@ -2175,7 +2175,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="E58" s="3">
         <v>1400</v>
@@ -2208,7 +2208,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3300</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
         <v>900</v>
